--- a/source_data/SourceData_EDFig7.xlsx
+++ b/source_data/SourceData_EDFig7.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); bins of the drawn Ru content</t>
+          <t>analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 5 bins of the drawn A_bed Ru content (A_bed_wt_pct)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -642,7 +642,7 @@
         <v>5000</v>
       </c>
       <c r="E4" t="n">
-        <v>7.110423493907948</v>
+        <v>7.110423493907959</v>
       </c>
     </row>
     <row r="5">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4798</v>
+        <v>0.3556</v>
       </c>
       <c r="D5" t="n">
         <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01433004794961779</v>
+        <v>-0.0942516738250303</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A_bed: u and r, supported bed</t>
+          <t>A_bed: u and r, commercial Ru/C bed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7998</v>
+        <v>0.6898</v>
       </c>
       <c r="D6" t="n">
         <v>5000</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3687787202002459</v>
+        <v>0.1786261991028901</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B: measured Ru catalysts, 90-94 % recovery</t>
+          <t>B: measured Ru catalysts, 90-97 % recovery</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9466</v>
       </c>
       <c r="D7" t="n">
         <v>5000</v>
       </c>
       <c r="E7" t="n">
-        <v>4.35034782150187</v>
+        <v>4.926524813946543</v>
       </c>
     </row>
     <row r="8">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="D8" t="n">
         <v>5000</v>
       </c>
       <c r="E8" t="n">
-        <v>7.40586957209078</v>
+        <v>7.774046410924601</v>
       </c>
     </row>
   </sheetData>
@@ -826,10 +826,10 @@
         <v>594</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003367003367003367</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1902356902356902</v>
+        <v>0.3434343434343434</v>
       </c>
     </row>
     <row r="5">
@@ -843,10 +843,10 @@
         <v>662</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01208459214501511</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2522658610271903</v>
+        <v>0.4078549848942598</v>
       </c>
     </row>
     <row r="6">
@@ -860,10 +860,10 @@
         <v>626</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02715654952076677</v>
+        <v>0.01277955271565495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3146964856230032</v>
+        <v>0.476038338658147</v>
       </c>
     </row>
     <row r="7">
@@ -877,10 +877,10 @@
         <v>638</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08150470219435736</v>
       </c>
       <c r="E7" t="n">
-        <v>0.493730407523511</v>
+        <v>0.658307210031348</v>
       </c>
     </row>
     <row r="8">
@@ -894,10 +894,10 @@
         <v>572</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1975524475524476</v>
+        <v>0.243006993006993</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5646853146853147</v>
+        <v>0.6940559440559441</v>
       </c>
     </row>
     <row r="9">
@@ -911,10 +911,10 @@
         <v>634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2586750788643533</v>
+        <v>0.4858044164037855</v>
       </c>
       <c r="E9" t="n">
-        <v>0.667192429022082</v>
+        <v>0.7649842271293376</v>
       </c>
     </row>
     <row r="10">
@@ -928,10 +928,10 @@
         <v>640</v>
       </c>
       <c r="D10" t="n">
-        <v>0.425</v>
+        <v>0.7515625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.796875</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="11">
@@ -945,10 +945,10 @@
         <v>634</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5788643533123028</v>
+        <v>0.88801261829653</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8722397476340694</v>
+        <v>0.9274447949526814</v>
       </c>
     </row>
   </sheetData>
@@ -1042,135 +1042,135 @@
         <v>0.9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.905</v>
+        <v>0.9087500000000001</v>
       </c>
       <c r="C4" t="n">
         <v>585</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1709401709401709</v>
+        <v>0.2085470085470086</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4205128205128205</v>
+        <v>0.4341880341880342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.905</v>
+        <v>0.9087500000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>0.91</v>
+        <v>0.9175</v>
       </c>
       <c r="C5" t="n">
         <v>603</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1575456053067993</v>
+        <v>0.2321724709784411</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4112769485903814</v>
+        <v>0.4461028192371476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.91</v>
+        <v>0.9175</v>
       </c>
       <c r="B6" t="n">
-        <v>0.915</v>
+        <v>0.92625</v>
       </c>
       <c r="C6" t="n">
         <v>634</v>
       </c>
       <c r="D6" t="n">
-        <v>0.165615141955836</v>
+        <v>0.2602523659305994</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4747634069400631</v>
+        <v>0.5488958990536278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.915</v>
+        <v>0.92625</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="C7" t="n">
         <v>634</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2050473186119874</v>
+        <v>0.2854889589905363</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5078864353312302</v>
+        <v>0.5993690851735016</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.9199999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9249999999999999</v>
+        <v>0.94375</v>
       </c>
       <c r="C8" t="n">
         <v>638</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2053291536050157</v>
+        <v>0.3072100313479624</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5078369905956113</v>
+        <v>0.6473354231974922</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.9249999999999999</v>
+        <v>0.94375</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9299999999999999</v>
+        <v>0.9525</v>
       </c>
       <c r="C9" t="n">
         <v>649</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2003081664098613</v>
+        <v>0.3235747303543914</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5562403697996918</v>
+        <v>0.7503852080123267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.9299999999999999</v>
+        <v>0.9525</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9349999999999999</v>
+        <v>0.9612499999999999</v>
       </c>
       <c r="C10" t="n">
         <v>640</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2546875</v>
+        <v>0.4171875</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6234375</v>
+        <v>0.8296875</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.9349999999999999</v>
+        <v>0.9612499999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="C11" t="n">
         <v>617</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2382495948136143</v>
+        <v>0.4376012965964344</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6482982171799028</v>
+        <v>0.8752025931928687</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); bins of the drawn Ru content</t>
+          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 5 bins of the drawn A_bed Ru content (A_bed_wt_pct)</t>
         </is>
       </c>
     </row>
@@ -1261,87 +1261,87 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>283</v>
+        <v>966</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.1966873706004141</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5159010600706714</v>
+        <v>0.6614906832298136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>1009</v>
+        <v>980</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005946481665014866</v>
+        <v>0.2724489795918367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5034687809712587</v>
+        <v>0.6520408163265307</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>1967</v>
+        <v>969</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1581087951194713</v>
+        <v>0.3219814241486068</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5292323335027961</v>
+        <v>0.6346749226006192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>836</v>
+        <v>1012</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3014354066985646</v>
+        <v>0.3527667984189723</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5322966507177034</v>
+        <v>0.6492094861660079</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" t="n">
         <v>10</v>
       </c>
-      <c r="B8" t="n">
-        <v>15</v>
-      </c>
       <c r="C8" t="n">
-        <v>905</v>
+        <v>1073</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4773480662983425</v>
+        <v>0.3960857409133271</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5093922651933702</v>
+        <v>0.6262814538676608</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig7.xlsx
+++ b/source_data/SourceData_EDFig7.xlsx
@@ -642,7 +642,7 @@
         <v>5000</v>
       </c>
       <c r="E4" t="n">
-        <v>7.110423493907959</v>
+        <v>7.110423493907948</v>
       </c>
     </row>
     <row r="5">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3556</v>
+        <v>0.419</v>
       </c>
       <c r="D5" t="n">
         <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0942516738250303</v>
+        <v>-0.052607023858255</v>
       </c>
     </row>
     <row r="6">
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6898</v>
+        <v>0.7192</v>
       </c>
       <c r="D6" t="n">
         <v>5000</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1786261991028901</v>
+        <v>0.2083140294419197</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B: measured Ru catalysts, 90-97 % recovery</t>
+          <t>B: measured Ru catalysts, 90-95.6 % recovery</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9466</v>
+        <v>0.947</v>
       </c>
       <c r="D7" t="n">
         <v>5000</v>
       </c>
       <c r="E7" t="n">
-        <v>4.926524813946543</v>
+        <v>4.97515807222581</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         <v>5000</v>
       </c>
       <c r="E8" t="n">
-        <v>7.774046410924601</v>
+        <v>7.774046410924589</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3434343434343434</v>
+        <v>0.2575757575757576</v>
       </c>
     </row>
     <row r="5">
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4078549848942598</v>
+        <v>0.3157099697885196</v>
       </c>
     </row>
     <row r="6">
@@ -860,10 +860,10 @@
         <v>626</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01277955271565495</v>
+        <v>0.007987220447284345</v>
       </c>
       <c r="E6" t="n">
-        <v>0.476038338658147</v>
+        <v>0.3929712460063898</v>
       </c>
     </row>
     <row r="7">
@@ -877,10 +877,10 @@
         <v>638</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08150470219435736</v>
+        <v>0.05329153605015674</v>
       </c>
       <c r="E7" t="n">
-        <v>0.658307210031348</v>
+        <v>0.5830721003134797</v>
       </c>
     </row>
     <row r="8">
@@ -894,10 +894,10 @@
         <v>572</v>
       </c>
       <c r="D8" t="n">
-        <v>0.243006993006993</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6940559440559441</v>
+        <v>0.6328671328671329</v>
       </c>
     </row>
     <row r="9">
@@ -911,10 +911,10 @@
         <v>634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4858044164037855</v>
+        <v>0.4148264984227129</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7649842271293376</v>
+        <v>0.7255520504731862</v>
       </c>
     </row>
     <row r="10">
@@ -928,10 +928,10 @@
         <v>640</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7515625</v>
+        <v>0.7015625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.875</v>
+        <v>0.8265625</v>
       </c>
     </row>
     <row r="11">
@@ -945,10 +945,10 @@
         <v>634</v>
       </c>
       <c r="D11" t="n">
-        <v>0.88801261829653</v>
+        <v>0.8659305993690851</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9274447949526814</v>
+        <v>0.9053627760252366</v>
       </c>
     </row>
   </sheetData>
@@ -1042,7 +1042,7 @@
         <v>0.9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9087500000000001</v>
+        <v>0.9069375000000001</v>
       </c>
       <c r="C4" t="n">
         <v>585</v>
@@ -1051,126 +1051,126 @@
         <v>0.2085470085470086</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4341880341880342</v>
+        <v>0.4256410256410256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.9087500000000001</v>
+        <v>0.9069375000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9175</v>
+        <v>0.913875</v>
       </c>
       <c r="C5" t="n">
         <v>603</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2321724709784411</v>
+        <v>0.2271973466003317</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4461028192371476</v>
+        <v>0.4278606965174129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.9175</v>
+        <v>0.913875</v>
       </c>
       <c r="B6" t="n">
-        <v>0.92625</v>
+        <v>0.9208125</v>
       </c>
       <c r="C6" t="n">
         <v>634</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2602523659305994</v>
+        <v>0.2365930599369085</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5488958990536278</v>
+        <v>0.5110410094637224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.92625</v>
+        <v>0.9208125</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9277500000000001</v>
       </c>
       <c r="C7" t="n">
         <v>634</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2854889589905363</v>
+        <v>0.2681388012618297</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5993690851735016</v>
+        <v>0.5441640378548895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9277500000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>0.94375</v>
+        <v>0.9346875</v>
       </c>
       <c r="C8" t="n">
         <v>638</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3072100313479624</v>
+        <v>0.2789968652037618</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6473354231974922</v>
+        <v>0.5768025078369906</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.94375</v>
+        <v>0.9346875</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9525</v>
+        <v>0.941625</v>
       </c>
       <c r="C9" t="n">
         <v>649</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3235747303543914</v>
+        <v>0.2896764252696456</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7503852080123267</v>
+        <v>0.6471494607087828</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.9525</v>
+        <v>0.941625</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9612499999999999</v>
+        <v>0.9485625</v>
       </c>
       <c r="C10" t="n">
         <v>640</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4171875</v>
+        <v>0.3703125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8296875</v>
+        <v>0.7328125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.9612499999999999</v>
+        <v>0.9485625</v>
       </c>
       <c r="B11" t="n">
-        <v>0.97</v>
+        <v>0.9555</v>
       </c>
       <c r="C11" t="n">
         <v>617</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4376012965964344</v>
+        <v>0.3598055105348461</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8752025931928687</v>
+        <v>0.7649918962722853</v>
       </c>
     </row>
   </sheetData>
@@ -1270,10 +1270,10 @@
         <v>966</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1966873706004141</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6614906832298136</v>
+        <v>0.5910973084886129</v>
       </c>
     </row>
     <row r="5">
@@ -1287,10 +1287,10 @@
         <v>980</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2724489795918367</v>
+        <v>0.2387755102040816</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6520408163265307</v>
+        <v>0.5928571428571429</v>
       </c>
     </row>
     <row r="6">
@@ -1304,10 +1304,10 @@
         <v>969</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3219814241486068</v>
+        <v>0.2930856553147575</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6346749226006192</v>
+        <v>0.5779153766769866</v>
       </c>
     </row>
     <row r="7">
@@ -1321,10 +1321,10 @@
         <v>1012</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3527667984189723</v>
+        <v>0.3231225296442688</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6492094861660079</v>
+        <v>0.5830039525691699</v>
       </c>
     </row>
     <row r="8">
@@ -1338,10 +1338,10 @@
         <v>1073</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3960857409133271</v>
+        <v>0.364398881640261</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6262814538676608</v>
+        <v>0.5619757688723206</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig7.xlsx
+++ b/source_data/SourceData_EDFig7.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/summary.json (P_Fe_cheaper), checked against analysis/nh3_mc_ru_actual_2026_10_06/draws.csv</t>
+          <t>analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/summary.json (P_Fe_cheaper), checked against analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -497,7 +497,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 log-spaced bins of u over the drawn range</t>
+          <t>analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 log-spaced bins of u over the drawn range</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 bins of r over the drawn range</t>
+          <t>analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 bins of r over the drawn range</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -533,7 +533,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 5 bins of the drawn A_bed Ru content (A_bed_wt_pct)</t>
+          <t>analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 5 bins of the drawn A_bed Ru content (A_bed_wt_pct)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/summary.json (P_Fe_cheaper), checked against analysis/nh3_mc_ru_actual_2026_10_06/draws.csv</t>
+          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/summary.json (P_Fe_cheaper), checked against analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
         <v>5000</v>
       </c>
       <c r="E4" t="n">
-        <v>7.110423493907948</v>
+        <v>5.463918119279948</v>
       </c>
     </row>
     <row r="5">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.419</v>
+        <v>0.0922</v>
       </c>
       <c r="D5" t="n">
         <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.052607023858255</v>
+        <v>-0.5180251352557468</v>
       </c>
     </row>
     <row r="6">
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7192</v>
+        <v>0.2066</v>
       </c>
       <c r="D6" t="n">
         <v>5000</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2083140294419197</v>
+        <v>-0.3292808370359186</v>
       </c>
     </row>
     <row r="7">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.947</v>
+        <v>0.9296</v>
       </c>
       <c r="D7" t="n">
         <v>5000</v>
       </c>
       <c r="E7" t="n">
-        <v>4.97515807222581</v>
+        <v>3.521751466152642</v>
       </c>
     </row>
     <row r="8">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.99</v>
+        <v>0.9806</v>
       </c>
       <c r="D8" t="n">
         <v>5000</v>
       </c>
       <c r="E8" t="n">
-        <v>7.774046410924589</v>
+        <v>6.195138426373696</v>
       </c>
     </row>
   </sheetData>
@@ -784,7 +784,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 log-spaced bins of u over the drawn range</t>
+          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 log-spaced bins of u over the drawn range</t>
         </is>
       </c>
     </row>
@@ -826,10 +826,10 @@
         <v>594</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.3265993265993266</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2575757575757576</v>
+        <v>0.7205387205387206</v>
       </c>
     </row>
     <row r="5">
@@ -843,10 +843,10 @@
         <v>662</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.5226586102719033</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3157099697885196</v>
+        <v>0.7809667673716012</v>
       </c>
     </row>
     <row r="6">
@@ -860,10 +860,10 @@
         <v>626</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007987220447284345</v>
+        <v>0.7140575079872205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3929712460063898</v>
+        <v>0.8769968051118211</v>
       </c>
     </row>
     <row r="7">
@@ -877,10 +877,10 @@
         <v>638</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05329153605015674</v>
+        <v>0.8730407523510971</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5830721003134797</v>
+        <v>0.9435736677115988</v>
       </c>
     </row>
     <row r="8">
@@ -894,10 +894,10 @@
         <v>572</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.9300699300699301</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6328671328671329</v>
+        <v>0.9545454545454546</v>
       </c>
     </row>
     <row r="9">
@@ -911,10 +911,10 @@
         <v>634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4148264984227129</v>
+        <v>0.9794952681388013</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7255520504731862</v>
+        <v>0.9858044164037855</v>
       </c>
     </row>
     <row r="10">
@@ -928,10 +928,10 @@
         <v>640</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7015625</v>
+        <v>0.99375</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8265625</v>
+        <v>0.996875</v>
       </c>
     </row>
     <row r="11">
@@ -945,10 +945,10 @@
         <v>634</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8659305993690851</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9053627760252366</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1006,7 +1006,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 bins of r over the drawn range</t>
+          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 bins of r over the drawn range</t>
         </is>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
         <v>585</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2085470085470086</v>
+        <v>0.705982905982906</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4256410256410256</v>
+        <v>0.8239316239316239</v>
       </c>
     </row>
     <row r="5">
@@ -1065,10 +1065,10 @@
         <v>603</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2271973466003317</v>
+        <v>0.6948590381426202</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4278606965174129</v>
+        <v>0.8192371475953566</v>
       </c>
     </row>
     <row r="6">
@@ -1082,10 +1082,10 @@
         <v>634</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2365930599369085</v>
+        <v>0.7429022082018928</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5110410094637224</v>
+        <v>0.889589905362776</v>
       </c>
     </row>
     <row r="7">
@@ -1099,10 +1099,10 @@
         <v>634</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2681388012618297</v>
+        <v>0.7886435331230284</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5441640378548895</v>
+        <v>0.9053627760252366</v>
       </c>
     </row>
     <row r="8">
@@ -1116,10 +1116,10 @@
         <v>638</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2789968652037618</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5768025078369906</v>
+        <v>0.9247648902821317</v>
       </c>
     </row>
     <row r="9">
@@ -1133,10 +1133,10 @@
         <v>649</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2896764252696456</v>
+        <v>0.8366718027734977</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6471494607087828</v>
+        <v>0.9599383667180277</v>
       </c>
     </row>
     <row r="10">
@@ -1150,10 +1150,10 @@
         <v>640</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3703125</v>
+        <v>0.8875</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7328125</v>
+        <v>0.9640625</v>
       </c>
     </row>
     <row r="11">
@@ -1167,10 +1167,10 @@
         <v>617</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3598055105348461</v>
+        <v>0.8865478119935171</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7649918962722853</v>
+        <v>0.9643435980551054</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 5 bins of the drawn A_bed Ru content (A_bed_wt_pct)</t>
+          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 5 bins of the drawn A_bed Ru content (A_bed_wt_pct)</t>
         </is>
       </c>
     </row>
@@ -1270,10 +1270,10 @@
         <v>966</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.7215320910973085</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5910973084886129</v>
+        <v>0.906832298136646</v>
       </c>
     </row>
     <row r="5">
@@ -1287,10 +1287,10 @@
         <v>980</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2387755102040816</v>
+        <v>0.7704081632653061</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.9102040816326531</v>
       </c>
     </row>
     <row r="6">
@@ -1304,10 +1304,10 @@
         <v>969</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2930856553147575</v>
+        <v>0.8018575851393189</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5779153766769866</v>
+        <v>0.9143446852425181</v>
       </c>
     </row>
     <row r="7">
@@ -1321,10 +1321,10 @@
         <v>1012</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3231225296442688</v>
+        <v>0.8359683794466403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5830039525691699</v>
+        <v>0.9130434782608695</v>
       </c>
     </row>
     <row r="8">
@@ -1338,10 +1338,10 @@
         <v>1073</v>
       </c>
       <c r="D8" t="n">
-        <v>0.364398881640261</v>
+        <v>0.8313140726933831</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5619757688723206</v>
+        <v>0.8956197576887233</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig7.xlsx
+++ b/source_data/SourceData_EDFig7.xlsx
@@ -627,7 +627,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>preregistered (pure-Ru benchmark bed)</t>
+          <t>benchmark (pure-Ru bed)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">

--- a/source_data/SourceData_EDFig7.xlsx
+++ b/source_data/SourceData_EDFig7.xlsx
@@ -10,8 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -433,7 +431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source Data for Extended Data Fig. 7 (Actual-Ru-catalyst Monte Carlo; renderer figures/extended_data/render_extended_data.py, tables figures/extended_data/ed_data.py)</t>
+          <t>Source Data for Extended Data Fig. 7 (Supported Ru/C against fused iron with measured rate laws: robustness; renderer figures/extended_data/render_extended_data.py, tables figures/extended_data/ed_data.py)</t>
         </is>
       </c>
     </row>
@@ -479,7 +477,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/summary.json (P_Fe_cheaper), checked against analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv</t>
+          <t>analysis/nh3_fe_inrange_kinetics_2026_10_19/robustness.csv</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -497,46 +495,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 log-spaced bins of u over the drawn range</t>
+          <t>analysis/nh3_fe_inrange_kinetics_2026_10_19/robustness.csv</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>panel c</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 bins of r over the drawn range</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>panel d</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 5 bins of the drawn A_bed Ru content (A_bed_wt_pct)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -549,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -593,140 +555,339 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/summary.json (P_Fe_cheaper), checked against analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv</t>
+          <t>source: analysis/nh3_fe_inrange_kinetics_2026_10_19/robustness.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>case</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>column</t>
+          <t>gap_0_global</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>P_Fe_cheaper</t>
+          <t>gap_12_global</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>draws</t>
+          <t>gap_0_KAAP</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>median_Ru_minus_Fe_USD_t</t>
+          <t>gap_12_KAAP</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>benchmark (pure-Ru bed)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ru_base</t>
-        </is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-3.826053</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2.132677</v>
       </c>
       <c r="D4" t="n">
-        <v>5000</v>
+        <v>-1.20899</v>
       </c>
       <c r="E4" t="n">
-        <v>5.463918119279948</v>
+        <v>1.945403</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A: u and r on the price, benchmark bed (Fig. 3d reading)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ru_A</t>
-        </is>
+          <t>Fe catalyst price x0.5</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-3.634238</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0922</v>
+        <v>2.397908</v>
       </c>
       <c r="D5" t="n">
-        <v>5000</v>
+        <v>-1.094379</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5180251352557468</v>
+        <v>2.119008</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A_bed: u and r, commercial Ru/C bed</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ru_A_bed</t>
-        </is>
+          <t>Fe catalyst price x2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-4.164929</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2066</v>
+        <v>1.671838</v>
       </c>
       <c r="D6" t="n">
-        <v>5000</v>
+        <v>-1.438211</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3292808370359186</v>
+        <v>1.598193</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B: measured Ru catalysts, 90-95.6 % recovery</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ru_B</t>
-        </is>
+          <t>Ru/C bed 430 kg/m3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-3.750308</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9296</v>
+        <v>2.156557</v>
       </c>
       <c r="D7" t="n">
-        <v>5000</v>
+        <v>-1.184166</v>
       </c>
       <c r="E7" t="n">
-        <v>3.521751466152642</v>
+        <v>1.961677</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0: measured Ru catalysts, no recovery</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ru_B0</t>
-        </is>
+          <t>Ru/C bed 550 kg/m3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-3.884606</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9806</v>
+        <v>2.113938</v>
       </c>
       <c r="D8" t="n">
-        <v>5000</v>
+        <v>-1.234844</v>
       </c>
       <c r="E8" t="n">
-        <v>6.195138426373696</v>
+        <v>1.932568</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>recovery 90%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-3.064683</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.261481</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.015299</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.040703</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ru price x0.7</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-4.009194</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.637106</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.301206</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.92172</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ru price x1.3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-3.642913</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.516255</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.155906</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.969087</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>catalyst life 5 y</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-3.650174</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.040343</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.25429</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.881025</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>catalyst life 15 y</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-3.905734</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.170367</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.235045</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.966253</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fe effectiveness 0.5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-7.174381</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.261461</v>
+      </c>
+      <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ru/C effectiveness 0.5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-2.650949</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.65856</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.936855</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.47282</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>converter premium x0</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.457895</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4.879207</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.298302</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.958289</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>converter premium x0.5</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-2.706487</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.394652</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.753646</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.451846</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>converter premium x2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-5.497613</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.172296</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.213325</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.932517</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>inlet-rate sizing</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-1.695184</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.310728</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.060598</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.36689</v>
       </c>
     </row>
   </sheetData>
@@ -740,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -784,564 +945,227 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 log-spaced bins of u over the drawn range</t>
+          <t>source: analysis/nh3_fe_inrange_kinetics_2026_10_19/robustness.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>u_low</t>
+          <t>case</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>u_high</t>
+          <t>breakeven_global</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>draws</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>P_Ru_wins_A_bed</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>P_Ru_wins_A</t>
+          <t>breakeven_KAAP</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>11</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
       </c>
       <c r="B4" t="n">
-        <v>13.29198523106423</v>
+        <v>0.064884</v>
       </c>
       <c r="C4" t="n">
-        <v>594</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3265993265993266</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7205387205387206</v>
+        <v>0.04568</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>13.29198523106423</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Fe catalyst price x0.5</t>
+        </is>
       </c>
       <c r="B5" t="n">
-        <v>16.06153376207542</v>
+        <v>0.059305</v>
       </c>
       <c r="C5" t="n">
-        <v>662</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5226586102719033</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.7809667673716012</v>
+        <v>0.040701</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>16.06153376207542</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Fe catalyst price x2</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>19.40815177761327</v>
+        <v>0.075123</v>
       </c>
       <c r="C6" t="n">
-        <v>626</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.7140575079872205</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8769968051118211</v>
+        <v>0.056192</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>19.40815177761327</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ru/C bed 430 kg/m3</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>23.45207879911715</v>
+        <v>0.06421200000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>638</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8730407523510971</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9435736677115988</v>
+        <v>0.045059</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>23.45207879911715</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ru/C bed 550 kg/m3</t>
+        </is>
       </c>
       <c r="B8" t="n">
-        <v>28.33860773051089</v>
+        <v>0.065412</v>
       </c>
       <c r="C8" t="n">
-        <v>572</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.9300699300699301</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.046169</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>28.33860773051089</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>recovery 90%</t>
+        </is>
       </c>
       <c r="B9" t="n">
-        <v>34.24330503844303</v>
+        <v>0.0598</v>
       </c>
       <c r="C9" t="n">
-        <v>634</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.9794952681388013</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.9858044164037855</v>
+        <v>0.040008</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>34.24330503844303</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ru price x0.7</t>
+        </is>
       </c>
       <c r="B10" t="n">
-        <v>41.37831862125564</v>
+        <v>0.096669</v>
       </c>
       <c r="C10" t="n">
-        <v>640</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.99375</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.996875</v>
+        <v>0.06869400000000001</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>41.37831862125564</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ru price x1.3</t>
+        </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>0.04824</v>
       </c>
       <c r="C11" t="n">
-        <v>634</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>panel c</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 8 bins of r over the drawn range</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>r_low</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>r_high</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>draws</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>P_Ru_wins_A_bed</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>P_Ru_wins_A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.9069375000000001</v>
-      </c>
-      <c r="C4" t="n">
-        <v>585</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.705982905982906</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8239316239316239</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.9069375000000001</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.913875</v>
-      </c>
-      <c r="C5" t="n">
-        <v>603</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.6948590381426202</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.8192371475953566</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.913875</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.9208125</v>
-      </c>
-      <c r="C6" t="n">
-        <v>634</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.7429022082018928</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.889589905362776</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.9208125</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.9277500000000001</v>
-      </c>
-      <c r="C7" t="n">
-        <v>634</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7886435331230284</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9053627760252366</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.9277500000000001</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9346875</v>
-      </c>
-      <c r="C8" t="n">
-        <v>638</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.7931034482758621</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9247648902821317</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.9346875</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.941625</v>
-      </c>
-      <c r="C9" t="n">
-        <v>649</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.8366718027734977</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.9599383667180277</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.941625</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.9485625</v>
-      </c>
-      <c r="C10" t="n">
-        <v>640</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.8875</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.9640625</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.9485625</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9555</v>
-      </c>
-      <c r="C11" t="n">
-        <v>617</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.8865478119935171</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.9643435980551054</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>panel d</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>source: analysis/nh3_mc_ru_actual_2026_10_06/nh3_1_2/draws.csv (Ru wins: Ru_A_bed &lt; Fe, or Ru_A &lt; Fe); 5 bins of the drawn A_bed Ru content (A_bed_wt_pct)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Ru_wt_pct_low</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Ru_wt_pct_high</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>draws</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>P_Ru_wins_A_bed</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>P_Ru_wins_A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>966</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.7215320910973085</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.906832298136646</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>980</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7704081632653061</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9102040816326531</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>969</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.8018575851393189</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9143446852425181</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1012</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8359683794466403</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9130434782608695</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1073</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.8313140726933831</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.8956197576887233</v>
+        <v>0.033594</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>catalyst life 5 y</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.066986</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.047974</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>catalyst life 15 y</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.063999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.044742</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fe effectiveness 0.5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.156519</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ru/C effectiveness 0.5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.026785</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.017564</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>converter premium x0</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.012313</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.007128</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>converter premium x0.5</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.036834</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.026391</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>converter premium x2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.115125</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.084332</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>inlet-rate sizing</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.02735</v>
       </c>
     </row>
   </sheetData>
